--- a/04_DESIGN_TABLES/DesignTable_3474.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_3474.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,61 @@
           <t>$COMMENT</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L1@DRIVE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C1HEX@HEX</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>C2HEX@HEX</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>D1@BORE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>D2@BORE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>THDMAJ_A@DRIVE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>THDMAJ_B@DRIVE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ORB_I3@DRIVE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ORB_THDL@DRIVE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ORB_GRVDIA@DRIVE</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -711,6 +766,150 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3474-08-08-NWO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3474-08-08-NWO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1 / hexes / bores from the Brennan TFA catalog p.9; ORB majors from the end library; adjustable-end I3 / thread length / groove from the 6801 row of the same ORB size</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3474-08-08-NWO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.9 alone; adjustable end data from the 6801 end library; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3474-10-10-NWO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3474-10-10-NWO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1 / hexes / bores from the Brennan TFA catalog p.9; ORB majors from the end library; adjustable-end I3 / thread length / groove from the 6801 row of the same ORB size</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3474-10-10-NWO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.9 alone; adjustable end data from the 6801 end library; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_3474.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_3474.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OMi 3474 - Design Table SKELETON (no dimensional source) | OMi catalog 7 SKUs | ALL MISSING | GENERATED 2026-09-23</t>
+          <t>OMi 3474 - Design Table | OMi catalog 9 SKUs | L1 / hexes / drills: Brennan TFA p.9 (BRENNAN) | adjustable end: 6801 end library | updated 2026-10-20 (batch 19 staging B_newspec)</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-04-04-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (1.47 / 0.563 / 0.563 / 0.172 / 0.172) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-04-04-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -04 7/16-20 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -543,7 +543,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): filled from the Brennan TFA catalog p.9 + the 6801 end library; gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-04 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -560,12 +595,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-06-06-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (1.56 / 0.688 / 0.688 / 0.297 / 0.297) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-06-06-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -06 9/16-18 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -580,7 +615,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): filled from the Brennan TFA catalog p.9 + the 6801 end library; gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-06 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -597,12 +667,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-12-12-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (2.330 / 1.250 / 1.250 / 0.609 / 0.609) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-12-12-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -12 1 1/16-12 (standard) = catalog B1 AORB / B2 ORB; own Brennan 3474-12-12-NWO STEP (09_STEP_FILES, sha256 c396aa02...b7736f37; tools/_out/newmasters_20261002/work/3474/evidence/pilot_measurement.txt): L1 2.3302 / C1 1.25 / C2 1.25 / drills 0.609 = the catalog (same maker, one source), I3 1.1401, undercut root 0.945 = the 6801 row; adjustable thread length 0.410 on the STEP vs 0.469 Air-Way 6801 row: built to Air-Way (dimension rule 2026-10-20, Air-Way first; Q-CONFLICT-ORBTHDL-12)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -617,7 +687,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): filled from the Brennan TFA catalog p.9 + the 6801 end library; gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud MEASURED on the own Brennan STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -634,12 +739,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-16-16-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (2.36 / 1.500 / 1.500 / 0.844 / 0.844) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-16-16-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -16 1 5/16-12 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,7 +759,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): filled from the Brennan TFA catalog p.9 + the 6801 end library; gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-16 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -671,12 +811,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-20-20-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (2.31 / 1.875 / 1.875 / 1.078 / 1.078) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-20-20-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -20 1 5/8-12 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -691,7 +831,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): filled from the Brennan TFA catalog p.9 + the 6801 end library; gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-20 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -708,12 +883,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-24-24-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (2.420 / 2.125 / 2.125 / 1.312 / 1.312) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-24-24-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -24 1 7/8-12 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -728,7 +903,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): filled from the Brennan TFA catalog p.9 + the 6801 end library; gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-24 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.756</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -745,12 +955,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-32-32-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (2.59 / 2.750 / 2.750 / 1.781 / 1.781) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-32-32-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -32 2 1/2-12 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -765,7 +975,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): filled from the Brennan TFA catalog p.9 + the 6801 end library; gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-32 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.381</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -782,12 +1027,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1 / hexes / bores from the Brennan TFA catalog p.9; ORB majors from the end library; adjustable-end I3 / thread length / groove from the 6801 row of the same ORB size</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1 / hexes / bores from the Brennan TFA catalog p.9; ORB majors from the end library; adjustable-end I3 / thread length / groove from the 6801 row of the same ORB size | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-08-08-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (1.560 / 0.875 / 0.875 / 0.391 / 0.391) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-08-08-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -08 3/4-16 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -802,7 +1047,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.9 alone; adjustable end data from the 6801 end library; marked DimSource BRENNAN</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): values unchanged (already staged 2026-10-18); gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-08 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: 2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.9 alone; adjustable end data from the 6801 end library; marked DimSource BRENNAN</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -854,12 +1099,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1 / hexes / bores from the Brennan TFA catalog p.9; ORB majors from the end library; adjustable-end I3 / thread length / groove from the 6801 row of the same ORB size</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1 / hexes / bores from the Brennan TFA catalog p.9; ORB majors from the end library; adjustable-end I3 / thread length / groove from the 6801 row of the same ORB size | 2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): L1@DRIVE / C1HEX@HEX / C2HEX@HEX / D1@BORE / D2@BORE = Brennan TFA catalog p.9 table 3474-NWO (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json TFA-p009-t06, verified) row 3474-10-10-NWO cols "L1 LGTH" / "C1 HEX" / "C2 HEX" / "B1 DRILL" / "B2 DRILL" (2.04 / 1.000 / 1.000 / 0.484 / 0.484) - BRENNAN-marked (user 2026-10-18 "yes use brennan but still differentiate"); ORB_I3@DRIVE / ORB_THDL@DRIVE / ORB_GRVDIA@DRIVE = DesignTable_6801.xlsx row 6801-10-10-NWO-FG (Air-Way; adjustable ORB stud of the same size, end library, Q-TRANSFER-ENDLIB = yes 2026-10-08); THDMAJ_A / THDMAJ_B = SAE J1926 -10 7/8-14 (standard) = catalog B1 AORB / B2 ORB</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -874,7 +1119,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.9 alone; adjustable end data from the 6801 end library; marked DimSource BRENNAN</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): values unchanged (already staged 2026-10-18); gate TOOLCHAIN cleared - gen_straight2 SPEC 3474 (adjustable ORB end NWO ported from the 2026-10-02 work, NWO_3474_TRANSFER on: stud transferred from the Brennan 6801-10 STEP); DataStatus MISSING -&gt; ASSUMED (one source) | was: 2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.9 alone; adjustable end data from the 6801 end library; marked DimSource BRENNAN</t>
         </is>
       </c>
       <c r="H11" t="n">
